--- a/outputs/reports/catboost_v2/evaluation.xlsx
+++ b/outputs/reports/catboost_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9969364807392223</v>
+        <v>0.99713153627268</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5206017004578156</v>
+        <v>0.5339739190116678</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9212962962962963</v>
+        <v>0.9163722025912838</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6652737150020894</v>
+        <v>0.6747614917606245</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9971872601688412</v>
+        <v>0.997394624254168</v>
       </c>
       <c r="G2" t="n">
-        <v>259867</v>
+        <v>259936</v>
       </c>
       <c r="H2" t="n">
-        <v>733</v>
+        <v>679</v>
       </c>
       <c r="I2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J2" t="n">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9822592095165004</v>
+        <v>0.9857038033190811</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8843746975729039</v>
+        <v>0.8597675931673048</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3089866156787763</v>
+        <v>0.3055449330783939</v>
       </c>
       <c r="E2" t="n">
-        <v>93.50564407619856</v>
+        <v>94.09776252345014</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9351851851851852</v>
+        <v>0.9411071849234394</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0631788282086584</v>
+        <v>0.06233746366834939</v>
       </c>
       <c r="I2" t="n">
-        <v>19.11920039207021</v>
+        <v>19.19788292176832</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9560185185185185</v>
+        <v>0.9599528857479388</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03189658469422878</v>
+        <v>0.03143764102956362</v>
       </c>
       <c r="M2" t="n">
-        <v>9.652556273717401</v>
+        <v>9.681756624445018</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9652777777777778</v>
+        <v>0.9681978798586572</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255582</v>
+        <v>255718</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001760687372350166</v>
+        <v>0.0001681539821209301</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2906</v>
+        <v>2977</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003441156228492774</v>
+        <v>0.002015451797111186</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>834</v>
+        <v>749</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004796163069544364</v>
+        <v>0.01068090787716956</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>405</v>
+        <v>340</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009876543209876543</v>
+        <v>0.02058823529411765</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02427184466019417</v>
+        <v>0.02714932126696833</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.06172839506172839</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05517241379310345</v>
+        <v>0.05357142857142857</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07627118644067797</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1476510067114094</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>948</v>
+        <v>938</v>
       </c>
       <c r="C11" t="n">
-        <v>748</v>
+        <v>719</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7890295358649789</v>
+        <v>0.7665245202558635</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/catboost_v2/evaluation.xlsx
+++ b/outputs/reports/catboost_v2/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.99713153627268</v>
+        <v>0.9964211618257262</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5339739190116678</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9163722025912838</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6747614917606245</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.997394624254168</v>
+        <v>0.9988280639616647</v>
       </c>
       <c r="G2" t="n">
-        <v>259936</v>
+        <v>38353</v>
       </c>
       <c r="H2" t="n">
-        <v>679</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="J2" t="n">
-        <v>778</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9857038033190811</v>
+        <v>0.8840862017633377</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8597675931673048</v>
+        <v>0.4766298090742189</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3055449330783939</v>
+        <v>0.2564766839378239</v>
       </c>
       <c r="E2" t="n">
-        <v>94.09776252345014</v>
+        <v>61.04778353483017</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9411071849234394</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06233746366834939</v>
+        <v>0.05757261410788381</v>
       </c>
       <c r="I2" t="n">
-        <v>19.19788292176832</v>
+        <v>13.7037037037037</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9599528857479388</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03143764102956362</v>
+        <v>0.03060165975103734</v>
       </c>
       <c r="M2" t="n">
-        <v>9.681756624445018</v>
+        <v>7.283950617283951</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9681978798586572</v>
+        <v>0.7283950617283951</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255718</v>
+        <v>38228</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001681539821209301</v>
+        <v>0.001674165533117087</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2977</v>
+        <v>128</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002015451797111186</v>
+        <v>0.046875</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>749</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01068090787716956</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02058823529411765</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>221</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02714932126696833</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06172839506172839</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1075268817204301</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2207792207792208</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>938</v>
+        <v>61</v>
       </c>
       <c r="C11" t="n">
-        <v>719</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7665245202558635</v>
+        <v>0.7868852459016393</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
